--- a/data/crate_projects_leads.xlsx
+++ b/data/crate_projects_leads.xlsx
@@ -4,16 +4,93 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Contact Inquiries" state="visible" r:id="rId3"/>
-    <sheet sheetId="2" name="Newsletter Subscriptions" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Contact Inquiries" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Newsletter Subscriptions" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Created At</t>
+  </si>
+  <si>
+    <t>Updated At</t>
+  </si>
+  <si>
+    <t>ID1</t>
+  </si>
+  <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>test@example.com</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>Test Company</t>
+  </si>
+  <si>
+    <t>web-development</t>
+  </si>
+  <si>
+    <t>2k-5k</t>
+  </si>
+  <si>
+    <t>asap</t>
+  </si>
+  <si>
+    <t>Test message</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>2026-09-12T10:08:22.160Z</t>
+  </si>
+  <si>
+    <t>2026-09-12T10:18:01.362Z</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -21,16 +98,25 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0EA5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -38,12 +124,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,9 +480,135 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="12" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
